--- a/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$111</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>GIH2XY</t>
+          <t>GIH37N</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -482,103 +482,2965 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.…</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH2XY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>MC2020</t>
+          <t>GIH37P</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.…</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AVV26M</t>
+          <t>GIH37Q</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VÅE</t>
+          <t>IDA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Saknar introfras</t>
+          <t>Prosa/rubrik före frasning</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Saknar introfras före lärandemålen</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.…</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>GIH37R</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande, utifrån den kunskapsbas som lagts i Idrott och hälsa I med didaktisk inr…</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GIH37S</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper i idrotts- och hälsovetenskap med foku…</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>GIH3AN</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.…</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>GIH3AP</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.…</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>IH1001</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen består av fyra delkurser med mål enligt nedanstående.…</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>IH1002</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen består av fyra delkurser med mål enligt nedanstående.…</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>IH1005</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om rörelse som eget kunskapsområde och som medel …</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>IH1020</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om och förståelse för humanbiologiska och socialp…</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>IH1029</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': ### Delkurser…</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>IH1062</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper och förståelse för fysiologiska och motivationsps…</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>IH1082</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten ska efter genomförd kurs kunna:…</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1082</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>IH1111</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Studenten ska efter genomförd kurs kunna:…</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>IH2002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>IDA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': ### Delkurser…</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>BKE223</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>KEA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om kemi.…</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BKE223</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>AMC22C</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter genomgången kurs självständigt kunna:…</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>AMC2A7</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>GMC22H</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska ha kunskap om byggnad och funktion hos den friska människokroppen.…</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>MC1072</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska ha kunskap om byggnad och funktion hos den friska människokroppen.…</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>MC1077</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska ha kunskaper inom klinisk mikrobiologi, allmän farmakologi och läkemedelsh…</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>MC1079</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig grundläggande kunskaper inom allmän farmakologi, läkemed…</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>MC2023</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>MCA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>GNV2KY</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>GNV367</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturvetenskap och teknik …</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>NV1024</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med denna kurs är att kursdeltagarna ska utveckla sin didaktiska medvetenhet och praktiska skick…</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>NV1027</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att deltagarna utvecklar kunskap om och förmåga att arbeta med hållbar utveckling.…</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>NV1035</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturorienterande ämnen oc…</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>NV1036</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig…</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>NV3001</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>NAV</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att kursdeltagaren…</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>ASA24J</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>ASA24K</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>ASA24L</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande under kursen ska tillägna sig fördjupade kunskaper om barn och ungas utve…</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>ASA24M</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik…</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>ASA24N</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>ASA266</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>ASA26U</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>ASA27E</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse **…</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>ASA28A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik…</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28A</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>ASA28Q</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig en djupare förståelse av åldrande utifrån socialgerontologisk…</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>ASA293</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>ASA2BA</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA2BA</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>GSA24U</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>GSA24V</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>GSA27Y</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>GSA2AF</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>GSA2BV</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': unskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>GSA2DW</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E3</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E4</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>GSA2E5</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>GSA2NA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>GSA2NC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Moment 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>GSA2RE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>GSA2SD</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>GSA2SE</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>GSA32Y</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GSA352</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse _…</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DM</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DN</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DP</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DQ</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DR</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>GSA3DS</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>GSA3FK</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>GSA3FL</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**…</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>GSA3HA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>SA1037</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>SA1040</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskaper inom Motiverande samtal (MI) med inriktning på…</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>SA1045</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>SA1048</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>SA2020</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall ha fördjupat sina kunskaper om vetenskaplig metod, evidens och utvärderi…</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>SA3008</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SAA</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>ASR22N</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna identifiera barnmorskelärarens roll i att planera och genomföra…</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>ASR25P</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>ASR25Q</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål…</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>ASR26S</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål…</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>ASR284</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>ASR285</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>ASR286</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>ASR296</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>ASR2AD</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>SR3001</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa och integrera kunskaper om barnmorskans arbetsfält och ansva…</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>SR3002</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om kvalitativa och kvantitativa metoder, utve…</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>SR3003</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupad förståelse för global sexuell och reproduktiv häls…</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>SR3004</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna utveckla och tillämpa ett i praktiken hållbart vetenskapligt fö…</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>SR3005</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska visa fördjupade kunskaper om barnmorskans arbetsfält och ansvarsområd…</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>SR3006</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska visa fördjupade metodkunskaper och fördjupad förmåga att integrera ku…</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>SR3007</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna visa fördjupade metodkunskaper och förmåga att integrera kunska…</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>SR3008</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde. …</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>SR3009</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>SR3010</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>SR3011</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>SR3012</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>SR3013</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>SR3014</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>SR3015</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SRP</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt ska fördjupa och…</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>AVV26M</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>VV2001</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om handledning och handledningssituationer som är spec…</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>VV3004</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Som övergripande mål ska studenten ha tillägnat sig kunskaper inom vårdvetenskaplig teori och metod, som förberedelse fö…</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>VV3006</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>VV3007</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>VV3009</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse…</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>VV3010</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
           <t>VV3011</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>VÅE</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Saknar introfras</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Saknar introfras före lärandemålen</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>VV3012</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap …</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>VV3014</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>VV3015</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>VV3017</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>VÅE</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap,…</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E5"/>
+  <autoFilter ref="A1:E111"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -588,6 +3450,218 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -958,7 +958,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>AMC2A7</t>
+          <t>GMC22H</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska ha kunskap om byggnad och funktion hos den friska människokroppen.…</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC2A7</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GMC22H</t>
+          <t>MC1072</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1000,19 +1000,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska ha kunskap om byggnad och funktion hos den friska människokroppen.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska ha kunskap om byggnad och funktion hos den friska människokroppen.…</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MC1072</t>
+          <t>MC1077</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1027,19 +1027,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska ha kunskap om byggnad och funktion hos den friska människokroppen.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska ha kunskaper inom klinisk mikrobiologi, allmän farmakologi och läkemedelsh…</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MC1077</t>
+          <t>MC1079</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1054,19 +1054,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska ha kunskaper inom klinisk mikrobiologi, allmän farmakologi och läkemedelsh…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig grundläggande kunskaper inom allmän farmakologi, läkemed…</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MC1079</t>
+          <t>MC2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig grundläggande kunskaper inom allmän farmakologi, läkemed…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MC2023</t>
+          <t>GNV2KY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MCA</t>
+          <t>NAV</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1108,19 +1108,19 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': .…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>GNV2KY</t>
+          <t>GNV367</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1135,19 +1135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturvetenskap och teknik …</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>GNV367</t>
+          <t>NV1024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1162,19 +1162,19 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturvetenskap och teknik …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med denna kurs är att kursdeltagarna ska utveckla sin didaktiska medvetenhet och praktiska skick…</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>NV1024</t>
+          <t>NV1027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1189,19 +1189,19 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med denna kurs är att kursdeltagarna ska utveckla sin didaktiska medvetenhet och praktiska skick…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att deltagarna utvecklar kunskap om och förmåga att arbeta med hållbar utveckling.…</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>NV1027</t>
+          <t>NV1035</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1216,19 +1216,19 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att deltagarna utvecklar kunskap om och förmåga att arbeta med hållbar utveckling.…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturorienterande ämnen oc…</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>NV1035</t>
+          <t>NV1036</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1243,19 +1243,19 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturorienterande ämnen oc…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig…</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>NV1036</t>
+          <t>NV3001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1270,24 +1270,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att kursdeltagaren…</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>NV3001</t>
+          <t>ASA24L</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NAV</t>
+          <t>SAA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1297,19 +1297,19 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att kursdeltagaren…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande under kursen ska tillägna sig fördjupade kunskaper om barn och ungas utve…</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>ASA24J</t>
+          <t>ASA24M</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1324,19 +1324,19 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik…</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24J</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>ASA24K</t>
+          <t>ASA24N</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1351,19 +1351,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24K</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>ASA24L</t>
+          <t>ASA28A</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1378,19 +1378,19 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande under kursen ska tillägna sig fördjupade kunskaper om barn och ungas utve…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik…</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28A</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>ASA24M</t>
+          <t>ASA28Q</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1405,19 +1405,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig en djupare förståelse av åldrande utifrån socialgerontologisk…</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28Q</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>ASA24N</t>
+          <t>GSA24V</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>ASA266</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': unskap och förståelse…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA266</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>ASA26U</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA26U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>ASA27E</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse **…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Moment 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA27E</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>ASA28A</t>
+          <t>GSA2SE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Efter avslutad kurs ska den studerande kunna:…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28A</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ASA28Q</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig en djupare förståelse av åldrande utifrån socialgerontologisk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>ASA293</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA293</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>ASA2BA</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA2BA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GSA24U</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24U</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA3FL</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GSA27Y</t>
+          <t>GSA3HA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA27Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>GSA2AF</t>
+          <t>SA1037</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2AF</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>SA1040</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,19 +1756,19 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': unskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskaper inom Motiverande samtal (MI) med inriktning på…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1783,19 +1783,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>GSA2E3</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1810,24 +1810,24 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall ha fördjupat sina kunskaper om vetenskaplig metod, evidens och utvärderi…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E3</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>GSA2E4</t>
+          <t>ASR22N</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1837,24 +1837,24 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna identifiera barnmorskelärarens roll i att planera och genomföra…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E4</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>GSA2E5</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1864,24 +1864,24 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2E5</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>GSA2NA</t>
+          <t>ASR25Q</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1891,24 +1891,24 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>ASR26S</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1918,24 +1918,24 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Moment 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>GSA2RE</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1945,24 +1945,24 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2RE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>GSA2SD</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1972,24 +1972,24 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>GSA2SE</t>
+          <t>ASR286</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1999,24 +1999,24 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>ASR296</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2026,24 +2026,24 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>GSA352</t>
+          <t>ASR2AD</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2053,24 +2053,24 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse _…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA352</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2080,24 +2080,24 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa och integrera kunskaper om barnmorskans arbetsfält och ansva…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2107,24 +2107,24 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om kvalitativa och kvantitativa metoder, utve…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GSA3DP</t>
+          <t>SR3003</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2134,24 +2134,24 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupad förståelse för global sexuell och reproduktiv häls…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DP</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GSA3DQ</t>
+          <t>SR3004</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2161,24 +2161,24 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna utveckla och tillämpa ett i praktiken hållbart vetenskapligt fö…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DQ</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>GSA3DR</t>
+          <t>SR3005</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2188,24 +2188,24 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska visa fördjupade kunskaper om barnmorskans arbetsfält och ansvarsområd…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DR</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>SR3006</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2215,24 +2215,24 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska visa fördjupade metodkunskaper och fördjupad förmåga att integrera ku…</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>GSA3FK</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2242,24 +2242,24 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna visa fördjupade metodkunskaper och förmåga att integrera kunska…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FK</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>GSA3FL</t>
+          <t>SR3008</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2269,24 +2269,24 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde. …</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>GSA3HA</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2296,24 +2296,24 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SA1037</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2323,24 +2323,24 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SA1040</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2350,24 +2350,24 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskaper inom Motiverande samtal (MI) med inriktning på…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SA1045</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2377,24 +2377,24 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1045</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>SR3013</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall ha fördjupat sina kunskaper om vetenskaplig metod, evidens och utvärderi…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SA3008</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,24 +2458,24 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': _Kunskap och förståelse_…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt ska fördjupa och…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>ASR22N</t>
+          <t>VV2001</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2485,24 +2485,24 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna identifiera barnmorskelärarens roll i att planera och genomföra…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om handledning och handledningssituationer som är spec…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>VV3004</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2512,24 +2512,24 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Som övergripande mål ska studenten ha tillägnat sig kunskaper inom vårdvetenskaplig teori och metod, som förberedelse fö…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>ASR25Q</t>
+          <t>VV3009</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2539,24 +2539,24 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Efter avslutad kurs ska studenten kunna:…</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>ASR26S</t>
+          <t>VV3010</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2566,24 +2566,24 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>VV3011</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2593,24 +2593,24 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2620,24 +2620,24 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap …</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>ASR286</t>
+          <t>VV3014</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2647,24 +2647,24 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>ASR296</t>
+          <t>VV3015</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2674,24 +2674,24 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>ASR2AD</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2701,746 +2701,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap,…</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>SR3001</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa och integrera kunskaper om barnmorskans arbetsfält och ansva…</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>SR3002</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om kvalitativa och kvantitativa metoder, utve…</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
-        <is>
-          <t>SR3003</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupad förståelse för global sexuell och reproduktiv häls…</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
-        <is>
-          <t>SR3004</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna utveckla och tillämpa ett i praktiken hållbart vetenskapligt fö…</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
-        <is>
-          <t>SR3005</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska visa fördjupade kunskaper om barnmorskans arbetsfält och ansvarsområd…</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
-        <is>
-          <t>SR3006</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska visa fördjupade metodkunskaper och fördjupad förmåga att integrera ku…</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
-        <is>
-          <t>SR3007</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna visa fördjupade metodkunskaper och förmåga att integrera kunska…</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
-        <is>
-          <t>SR3008</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde. …</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>SR3009</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>SR3010</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>SR3011</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
-        <is>
-          <t>SR3012</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>SR3013</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>SR3014</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>SR3015</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>SRP</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt ska fördjupa och…</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>AVV26M</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kunskap och förståelse…</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AVV26M</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>VV2001</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om handledning och handledningssituationer som är spec…</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>VV3004</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Som övergripande mål ska studenten ha tillägnat sig kunskaper inom vårdvetenskaplig teori och metod, som förberedelse fö…</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>VV3006</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
-        </is>
-      </c>
-      <c r="E103" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3006</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>VV3007</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse**…</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3007</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>VV3009</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Kunskap och förståelse…</t>
-        </is>
-      </c>
-      <c r="E105" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>VV3010</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
-        </is>
-      </c>
-      <c r="E106" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>VV3011</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>VV3012</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap …</t>
-        </is>
-      </c>
-      <c r="E108" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>VV3014</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
-        </is>
-      </c>
-      <c r="E109" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>VV3015</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap,…</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E111"/>
+  <autoFilter ref="A1:E84"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -3608,60 +2879,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A85" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A86" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A87" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A88" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A89" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A90" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A92" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A93" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A94" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A95" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A96" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A97" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId194"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A99" r:id="rId195"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId196"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A100" r:id="rId197"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId198"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A101" r:id="rId199"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId200"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A102" r:id="rId201"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A103" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A105" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A106" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A107" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A108" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A109" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A110" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A111" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId220"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1417,7 +1417,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>GSA24V</t>
+          <t>GSA2BV</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1432,19 +1432,19 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter avslutad kurs kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': unskap och förståelse…</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA24V</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>GSA2BV</t>
+          <t>GSA2DW</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1459,19 +1459,19 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': unskap och förståelse…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>GSA2DW</t>
+          <t>GSA2NC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Moment 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>GSA2NC</t>
+          <t>GSA32Y</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1513,19 +1513,19 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Moment 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>GSA2SE</t>
+          <t>GSA3DM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1540,19 +1540,19 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Efter avslutad kurs ska den studerande kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2SE</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>GSA32Y</t>
+          <t>GSA3DN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1567,19 +1567,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>GSA3DM</t>
+          <t>GSA3DS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1594,19 +1594,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>GSA3DN</t>
+          <t>GSA3FL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1621,19 +1621,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**…</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>GSA3DS</t>
+          <t>GSA3HA</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1648,19 +1648,19 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>GSA3FL</t>
+          <t>SA1037</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1675,19 +1675,19 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>GSA3HA</t>
+          <t>SA1040</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1702,19 +1702,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskaper inom Motiverande samtal (MI) med inriktning på…</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>SA1037</t>
+          <t>SA1048</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1729,19 +1729,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>SA1040</t>
+          <t>SA2020</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskaper inom Motiverande samtal (MI) med inriktning på…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall ha fördjupat sina kunskaper om vetenskaplig metod, evidens och utvärderi…</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>SA1048</t>
+          <t>ASR22N</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1783,24 +1783,24 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna identifiera barnmorskelärarens roll i att planera och genomföra…</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>SA2020</t>
+          <t>ASR25P</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SAA</t>
+          <t>SRP</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1810,19 +1810,19 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall ha fördjupat sina kunskaper om vetenskaplig metod, evidens och utvärderi…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>ASR22N</t>
+          <t>ASR25Q</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1837,19 +1837,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna identifiera barnmorskelärarens roll i att planera och genomföra…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål…</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>ASR25P</t>
+          <t>ASR26S</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1864,19 +1864,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål…</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>ASR25Q</t>
+          <t>ASR284</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>ASR26S</t>
+          <t>ASR285</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1918,19 +1918,19 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>ASR284</t>
+          <t>ASR286</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1945,19 +1945,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>ASR285</t>
+          <t>ASR296</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1972,19 +1972,19 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>ASR286</t>
+          <t>ASR2AD</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1999,19 +1999,19 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>ASR296</t>
+          <t>SR3001</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2026,19 +2026,19 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa och integrera kunskaper om barnmorskans arbetsfält och ansva…</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>ASR2AD</t>
+          <t>SR3002</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2053,19 +2053,19 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om kvalitativa och kvantitativa metoder, utve…</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>SR3001</t>
+          <t>SR3003</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2080,19 +2080,19 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa och integrera kunskaper om barnmorskans arbetsfält och ansva…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupad förståelse för global sexuell och reproduktiv häls…</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>SR3002</t>
+          <t>SR3004</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2107,19 +2107,19 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om kvalitativa och kvantitativa metoder, utve…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna utveckla och tillämpa ett i praktiken hållbart vetenskapligt fö…</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>SR3003</t>
+          <t>SR3005</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2134,19 +2134,19 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupad förståelse för global sexuell och reproduktiv häls…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska visa fördjupade kunskaper om barnmorskans arbetsfält och ansvarsområd…</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>SR3004</t>
+          <t>SR3006</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2161,19 +2161,19 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna utveckla och tillämpa ett i praktiken hållbart vetenskapligt fö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska visa fördjupade metodkunskaper och fördjupad förmåga att integrera ku…</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>SR3005</t>
+          <t>SR3007</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2188,19 +2188,19 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska visa fördjupade kunskaper om barnmorskans arbetsfält och ansvarsområd…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna visa fördjupade metodkunskaper och förmåga att integrera kunska…</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>SR3006</t>
+          <t>SR3008</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2215,19 +2215,19 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska visa fördjupade metodkunskaper och fördjupad förmåga att integrera ku…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde. …</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>SR3007</t>
+          <t>SR3009</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2242,19 +2242,19 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna visa fördjupade metodkunskaper och förmåga att integrera kunska…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>SR3008</t>
+          <t>SR3010</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2269,19 +2269,19 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde. …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>SR3009</t>
+          <t>SR3011</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2296,19 +2296,19 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>SR3010</t>
+          <t>SR3012</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2323,19 +2323,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>SR3011</t>
+          <t>SR3013</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>SR3012</t>
+          <t>SR3014</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2377,19 +2377,19 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>SR3013</t>
+          <t>SR3015</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2404,24 +2404,24 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt ska fördjupa och…</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>SR3014</t>
+          <t>VV2001</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2431,24 +2431,24 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om handledning och handledningssituationer som är spec…</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>SR3015</t>
+          <t>VV3004</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SRP</t>
+          <t>VÅE</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2458,19 +2458,19 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt ska fördjupa och…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Som övergripande mål ska studenten ha tillägnat sig kunskaper inom vårdvetenskaplig teori och metod, som förberedelse fö…</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>VV2001</t>
+          <t>VV3010</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2485,19 +2485,19 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om handledning och handledningssituationer som är spec…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>VV3004</t>
+          <t>VV3011</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2512,19 +2512,19 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Som övergripande mål ska studenten ha tillägnat sig kunskaper inom vårdvetenskaplig teori och metod, som förberedelse fö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>VV3009</t>
+          <t>VV3012</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2539,19 +2539,19 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': **Efter avslutad kurs ska studenten kunna:…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap …</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3009</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>VV3010</t>
+          <t>VV3014</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2566,19 +2566,19 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>VV3011</t>
+          <t>VV3015</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2593,19 +2593,19 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>VV3012</t>
+          <t>VV3017</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -2620,98 +2620,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap …</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap,…</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>VV3014</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>VV3015</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>VV3017</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>VÅE</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap,…</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="inlineStr">
-        <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E84"/>
+  <autoFilter ref="A1:E81"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -2873,12 +2792,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2629,8 +2629,89 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>FHV0001</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är ge en introduktion till vetenskapsteori och forskarens roll i samhället samt ge kunskap i fo…</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>FHV0002</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att ge kunskap om metod för och värdering av kvantitativa, kvalitativa och integrativa/-mixad-…</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0002</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>FHV0003</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>VÅRDVETS</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att ge kunskap om teoretiska ramverk, designer, metoder och faktorer som har betydelse för f…</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0003</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E81"/>
+  <autoFilter ref="A1:E84"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
@@ -2792,6 +2873,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Introfras" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$E$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Introfras'!$A$1:$G$84</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -432,14 +432,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="70" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
+    <col width="70" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,15 +457,25 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Fastställd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Reviderad</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Problem</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Detalj</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Länk</t>
         </is>
@@ -482,15 +494,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.…</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37N</t>
         </is>
@@ -509,15 +527,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.…</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37P</t>
         </is>
@@ -536,15 +560,21 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.…</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37Q</t>
         </is>
@@ -563,15 +593,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande, utifrån den kunskapsbas som lagts i Idrott och hälsa I med didaktisk inr…</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37R</t>
         </is>
@@ -590,15 +626,21 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+          <t>2023-12-05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig fördjupade kunskaper i idrotts- och hälsovetenskap med foku…</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH37S</t>
         </is>
@@ -617,15 +659,21 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.…</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AN</t>
         </is>
@@ -644,15 +692,21 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande utvecklar grundläggande kunskaper om idrott och hälsa.…</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GIH3AP</t>
         </is>
@@ -671,15 +725,21 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen består av fyra delkurser med mål enligt nedanstående.…</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1001</t>
         </is>
@@ -698,15 +758,21 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen består av fyra delkurser med mål enligt nedanstående.…</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1002</t>
         </is>
@@ -725,15 +791,21 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om rörelse som eget kunskapsområde och som medel …</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1005</t>
         </is>
@@ -752,15 +824,25 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2011-01-26</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>2012-10-31</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om och förståelse för humanbiologiska och socialp…</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1020</t>
         </is>
@@ -779,15 +861,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+          <t>2011-03-30</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': ### Delkurser…</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1029</t>
         </is>
@@ -806,15 +894,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2012-12-05</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>2013-11-25</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper och förståelse för fysiologiska och motivationsps…</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1062</t>
         </is>
@@ -833,15 +931,25 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-09-03</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>2014-01-23</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenten ska efter genomförd kurs kunna:…</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1082</t>
         </is>
@@ -860,15 +968,21 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+          <t>2014-12-09</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Studenten ska efter genomförd kurs kunna:…</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH1111</t>
         </is>
@@ -887,15 +1001,21 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+          <t>2011-01-26</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': ### Delkurser…</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=IH2002</t>
         </is>
@@ -914,15 +1034,21 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
+          <t>2021-02-17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om kemi.…</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=BKE223</t>
         </is>
@@ -941,15 +1067,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2018-09-27</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>2018-10-22</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Den studerande ska efter genomgången kurs självständigt kunna:…</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=AMC22C</t>
         </is>
@@ -968,15 +1104,25 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2018-04-12</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>2018-04-16</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska ha kunskap om byggnad och funktion hos den friska människokroppen.…</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GMC22H</t>
         </is>
@@ -995,15 +1141,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-09-09</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>2014-01-22</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska ha kunskap om byggnad och funktion hos den friska människokroppen.…</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1072</t>
         </is>
@@ -1022,15 +1178,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+          <t>2015-02-12</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska ha kunskaper inom klinisk mikrobiologi, allmän farmakologi och läkemedelsh…</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1077</t>
         </is>
@@ -1049,15 +1211,25 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2015-06-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>2015-08-18</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig grundläggande kunskaper inom allmän farmakologi, läkemed…</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC1079</t>
         </is>
@@ -1076,15 +1248,21 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
+          <t>2015-02-12</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': .…</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=MC2023</t>
         </is>
@@ -1103,15 +1281,21 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+          <t>2020-11-26</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV2KY</t>
         </is>
@@ -1130,15 +1314,21 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+          <t>2023-09-11</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturvetenskap och teknik …</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GNV367</t>
         </is>
@@ -1157,15 +1347,25 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2012-10-11</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>2014-02-12</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande syftet med denna kurs är att kursdeltagarna ska utveckla sin didaktiska medvetenhet och praktiska skick…</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1024</t>
         </is>
@@ -1184,15 +1384,25 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2013-03-15</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>2014-02-12</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att deltagarna utvecklar kunskap om och förmåga att arbeta med hållbar utveckling.…</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1027</t>
         </is>
@@ -1211,15 +1421,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+          <t>2017-08-24</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig grundläggande kunskaper i och om naturorienterande ämnen oc…</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1035</t>
         </is>
@@ -1238,15 +1454,21 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+          <t>2017-09-28</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig…</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV1036</t>
         </is>
@@ -1265,15 +1487,21 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+          <t>2016-03-03</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att kursdeltagaren…</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=NV3001</t>
         </is>
@@ -1292,15 +1520,25 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2020-02-13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>2020-05-04</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande under kursen ska tillägna sig fördjupade kunskaper om barn och ungas utve…</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24L</t>
         </is>
@@ -1319,15 +1557,25 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2020-02-19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>2020-06-24</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik…</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24M</t>
         </is>
@@ -1346,15 +1594,25 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2020-03-02</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>2020-05-20</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens…</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA24N</t>
         </is>
@@ -1373,15 +1631,21 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+          <t>2022-10-25</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande tillägnar sig kunskaper om välfärdsteknik…</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28A</t>
         </is>
@@ -1400,15 +1664,21 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+          <t>2022-12-12</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten ska tillägna sig en djupare förståelse av åldrande utifrån socialgerontologisk…</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASA28Q</t>
         </is>
@@ -1427,15 +1697,25 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2019-10-29</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>2023-01-19</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': unskap och förståelse…</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2BV</t>
         </is>
@@ -1454,15 +1734,25 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2020-02-20</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>2023-11-30</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2DW</t>
         </is>
@@ -1481,15 +1771,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': **Moment 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA2NC</t>
         </is>
@@ -1508,15 +1804,21 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
+          <t>2023-02-07</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA32Y</t>
         </is>
@@ -1535,15 +1837,21 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DM</t>
         </is>
@@ -1562,15 +1870,21 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DN</t>
         </is>
@@ -1589,15 +1903,21 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
+          <t>2024-12-10</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 5 högskolepoäng**…</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3DS</t>
         </is>
@@ -1616,15 +1936,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
+          <t>2025-03-24</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': **Modul 1. Campusförlagd utbildning, 4,5 högskolepoäng**…</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3FL</t>
         </is>
@@ -1643,15 +1969,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper och färdigheter inom socialt arbete m…</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=GSA3HA</t>
         </is>
@@ -1670,15 +2002,21 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
+          <t>2015-03-11</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1037</t>
         </is>
@@ -1697,15 +2035,21 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
+          <t>2016-05-20</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskaper inom Motiverande samtal (MI) med inriktning på…</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1040</t>
         </is>
@@ -1724,15 +2068,21 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
+          <t>2017-11-30</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet med kursen är att den studerande ska tillägna sig kunskaper om välfärdsinsatser på individ-, grup…</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA1048</t>
         </is>
@@ -1751,15 +2101,21 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
+          <t>2014-12-23</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten skall ha fördjupat sina kunskaper om vetenskaplig metod, evidens och utvärderi…</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SA2020</t>
         </is>
@@ -1778,15 +2134,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+          <t>2018-12-06</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna identifiera barnmorskelärarens roll i att planera och genomföra…</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR22N</t>
         </is>
@@ -1805,15 +2167,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den…</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25P</t>
         </is>
@@ -1832,15 +2200,21 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål…</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR25Q</t>
         </is>
@@ -1859,15 +2233,21 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
+          <t>2021-03-08</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål…</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR26S</t>
         </is>
@@ -1886,15 +2266,21 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR284</t>
         </is>
@@ -1913,15 +2299,21 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR285</t>
         </is>
@@ -1940,15 +2332,21 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
+          <t>2022-06-16</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR286</t>
         </is>
@@ -1967,15 +2365,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
+          <t>2023-06-15</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR296</t>
         </is>
@@ -1994,15 +2398,21 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
+          <t>2024-02-27</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid komplicerad graviditet, förlossning …</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=ASR2AD</t>
         </is>
@@ -2021,15 +2431,21 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa och integrera kunskaper om barnmorskans arbetsfält och ansva…</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3001</t>
         </is>
@@ -2048,15 +2464,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om kvalitativa och kvantitativa metoder, utve…</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3002</t>
         </is>
@@ -2075,15 +2497,21 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska utveckla fördjupad förståelse för global sexuell och reproduktiv häls…</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3003</t>
         </is>
@@ -2102,15 +2530,21 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna utveckla och tillämpa ett i praktiken hållbart vetenskapligt fö…</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3004</t>
         </is>
@@ -2129,15 +2563,21 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska visa fördjupade kunskaper om barnmorskans arbetsfält och ansvarsområd…</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3005</t>
         </is>
@@ -2156,15 +2596,21 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska visa fördjupade metodkunskaper och fördjupad förmåga att integrera ku…</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3006</t>
         </is>
@@ -2183,15 +2629,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
+          <t>2016-10-05</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska kunna visa fördjupade metodkunskaper och förmåga att integrera kunska…</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3007</t>
         </is>
@@ -2210,15 +2662,21 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska tillägna sig kunskaper om barnmorskans arbetsfält och ansvarsområde. …</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3008</t>
         </is>
@@ -2237,15 +2695,25 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
+          <t>2017-10-05</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska fördjupa sina kunskaper om sexuell och reproduktiv hälsa som en mänsk…</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3009</t>
         </is>
@@ -2264,15 +2732,25 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
+          <t>2017-10-05</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3010</t>
         </is>
@@ -2291,15 +2769,25 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
+          <t>2017-05-22</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande utifrån ett hållbarhetsperspektiv ska tillämpa, fördjupa och integrera sin…</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3011</t>
         </is>
@@ -2318,15 +2806,21 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande ska tillämpa, fördjupa och integrera sina teoretiska och kliniska kunskape…</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3012</t>
         </is>
@@ -2345,15 +2839,21 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
+          <t>2016-10-12</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande genom ett självständigt vetenskapligt arbetssätt kan hantera och utveckla…</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3013</t>
         </is>
@@ -2372,15 +2872,25 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
+          <t>2017-05-22</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt kan tillämpa, ytt…</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3014</t>
         </is>
@@ -2399,15 +2909,25 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2016-10-12</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
+          <t>2018-01-10</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande med hög grad av systematik och kritiskt förhållningssätt ska fördjupa och…</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=SR3015</t>
         </is>
@@ -2426,15 +2946,25 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2009-04-21</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
+          <t>2012-03-05</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten tillägnar sig kunskaper om handledning och handledningssituationer som är spec…</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV2001</t>
         </is>
@@ -2453,15 +2983,25 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2008-03-03</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
+          <t>2015-10-02</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Som övergripande mål ska studenten ha tillägnat sig kunskaper inom vårdvetenskaplig teori och metod, som förberedelse fö…</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3004</t>
         </is>
@@ -2480,15 +3020,25 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2009-12-14</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
+          <t>2013-08-26</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3010</t>
         </is>
@@ -2507,15 +3057,25 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2010-06-01</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
+          <t>2010-10-18</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursen har som övergripande mål att studenten ska fördjupa och integrera sina teoretiska och praktiska kunskaper inom äm…</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3011</t>
         </is>
@@ -2534,15 +3094,25 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2012-01-12</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
+          <t>2018-11-14</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap …</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3012</t>
         </is>
@@ -2561,15 +3131,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
+          <t>2014-03-06</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3014</t>
         </is>
@@ -2588,15 +3164,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
+          <t>2015-02-05</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande har fördjupade kunskaper om implementering av forskningsbaserad kunskap i…</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3015</t>
         </is>
@@ -2615,15 +3197,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
+          <t>2015-12-22</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Genom ett självständigt arbete erhålla fördjupad kunskap inom ett komplext problemområde med relevans för vårdvetenskap,…</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=VV3017</t>
         </is>
@@ -2642,15 +3230,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
+          <t>2018-01-25</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är ge en introduktion till vetenskapsteori och forskarens roll i samhället samt ge kunskap i fo…</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0001</t>
         </is>
@@ -2669,15 +3263,25 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
+          <t>2018-03-28</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
+          <t>2022-09-28</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
           <t>Lärandemål inleds inte med 'Efter ...': Det övergripande målet är att ge kunskap om metod för och värdering av kvantitativa, kvalitativa och integrativa/-mixad-…</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0002</t>
         </is>
@@ -2696,189 +3300,195 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Prosa/rubrik före frasning</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
+          <t>2018-11-01</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Prosa/rubrik före frasning</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att ge kunskap om teoretiska ramverk, designer, metoder och faktorer som har betydelse för f…</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr">
         <is>
           <t>https://www.du.se/sv/utbildning/kurser/kursplan/?code=FHV0003</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E84"/>
+  <autoFilter ref="A1:G84"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E2" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G2" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G3" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G4" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A7" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A8" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G8" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G9" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G11" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G12" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G13" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G14" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G15" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G16" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G17" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G18" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G19" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G20" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G21" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G22" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G23" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G24" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G25" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E26" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G26" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E27" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E28" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G28" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E29" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E30" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E31" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G31" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E32" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G32" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E33" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G33" r:id="rId64"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E34" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G34" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E35" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G35" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E36" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G36" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E37" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G37" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G38" r:id="rId74"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G39" r:id="rId76"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G40" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G41" r:id="rId80"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G42" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E43" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G43" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E44" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G46" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G47" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E50" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E51" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G51" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E52" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G52" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E53" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G53" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E54" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G54" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E55" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G55" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E56" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G56" r:id="rId110"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E57" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G57" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A58" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E58" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G58" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E59" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G59" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A60" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E60" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G60" r:id="rId118"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A61" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E61" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G61" r:id="rId120"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A62" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E62" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G62" r:id="rId122"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E63" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G63" r:id="rId124"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A64" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E64" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G64" r:id="rId126"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A65" r:id="rId127"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E65" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G65" r:id="rId128"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A66" r:id="rId129"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E66" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G66" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A67" r:id="rId131"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E67" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G67" r:id="rId132"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A68" r:id="rId133"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E68" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId134"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A69" r:id="rId135"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E69" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId136"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A70" r:id="rId137"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E70" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A71" r:id="rId139"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E71" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A72" r:id="rId141"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E72" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A73" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E73" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E74" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId146"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A75" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E75" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId148"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A76" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E76" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId150"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A77" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E77" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId152"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A78" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E78" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId154"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E79" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G79" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A80" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E80" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G80" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A81" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E81" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G81" r:id="rId160"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A82" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G82" r:id="rId162"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A83" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G83" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A84" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G84" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
@@ -2013,7 +2013,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripandemål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention samt…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att studenten inhämtat kunskap om teoretisk grund och evidensbas för återfallsprevention sam…</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">

--- a/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
+++ b/vault-dalarna-university/02 IHV/Analys/Introfras.xlsx
@@ -2747,7 +2747,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripade mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, fö…</t>
+          <t>Lärandemål inleds inte med 'Efter ...': Kursens övergripande mål är att den studerande ska förstå förlopp och processer vid normal och komplicerad graviditet, f…</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
